--- a/examples/03-formulas.xlsx
+++ b/examples/03-formulas.xlsx
@@ -8,11 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="Orders" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Settings" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lookup" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Jan" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Feb" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mar" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Budget" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Settings" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet name="Summary" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="VAT">Settings!$B$1</definedName>
+    <definedName name="OrderProducts">Orders!$A$2:$A$7</definedName>
+    <definedName name="Discount" localSheetId="1">0.05</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -154,6 +161,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Analyst</author>
+    <author>Finance</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
@@ -161,20 +169,40 @@
         <t>Product names come from the catalog</t>
       </text>
     </comment>
+    <comment ref="D1" authorId="1" shapeId="0">
+      <text>
+        <t>Total = Quantity × Price
+VAT is added in the summary</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Orders" displayName="Orders" ref="A1:D6" headerRowCount="1">
-  <autoFilter ref="A1:D6"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OrderList" displayName="OrderList" ref="A1:E7" headerRowCount="1">
+  <autoFilter ref="A1:E7"/>
+  <tableColumns count="5">
     <tableColumn id="1" name="Product"/>
     <tableColumn id="2" name="Quantity"/>
     <tableColumn id="3" name="Price"/>
     <tableColumn id="4" name="Total"/>
+    <tableColumn id="5" name="Category"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="BudgetTable" displayName="BudgetTable" ref="A3:D7" headerRowCount="1" totalsRowCount="1">
+  <autoFilter ref="A3:D7"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Column1" totalsRowLabel="Total"/>
+    <tableColumn id="2" name="Column2" totalsRowFunction="sum"/>
+    <tableColumn id="3" name="Column3" totalsRowFunction="sum"/>
+    <tableColumn id="4" name="Column4" totalsRowFunction="sum"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
 </file>
 
@@ -467,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +519,12 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>Doubled</t>
         </is>
@@ -513,8 +546,13 @@
         <f>B2*C2</f>
         <v/>
       </c>
-      <c r="F2">
-        <f t="array" ref="F2:F6">B2:B6*2</f>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="G2">
+        <f t="array" ref="G2:G7">B2:B7*2</f>
         <v/>
       </c>
     </row>
@@ -534,6 +572,11 @@
         <f>B3*C3</f>
         <v/>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,6 +594,11 @@
         <f>B4*C4</f>
         <v/>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -568,6 +616,11 @@
         <f>B5*C5</f>
         <v/>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -585,50 +638,107 @@
         <f>B6*C6</f>
         <v/>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sum</t>
-        </is>
+          <t>Консультація</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1200</v>
       </c>
       <c r="D7">
-        <f>SUM(D2:D6)</f>
-        <v/>
+        <f>B7*C7</f>
+        <v/>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Послуги</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Average price</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="D8">
-        <f>AVERAGE(C2:C6)</f>
+        <f>SUM(D2:D7)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Average price</t>
+        </is>
+      </c>
+      <c r="D9">
+        <f>AVERAGE(C2:C7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>With VAT</t>
         </is>
       </c>
-      <c r="D9">
-        <f>D7*(1+VAT)</f>
+      <c r="D10">
+        <f>D8*(1+VAT)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Hardware total</t>
+        </is>
+      </c>
+      <c r="D11">
+        <f>SUMIFS(D2:D7,E2:E7,"Hardware")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Orders over 1000</t>
+        </is>
+      </c>
+      <c r="D12">
+        <f>COUNTIF(D2:D7,"&gt;1000")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Go to the summary</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId1"/>
+    <hyperlink ref="A15" location="Summary!A1" tooltip="Summary sheet"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -639,6 +749,172 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Found price</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Row</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Due</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Widget</t>
+        </is>
+      </c>
+      <c r="B2">
+        <f>VLOOKUP(A2,Orders!$A$2:$C$7,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="C2">
+        <f>MATCH(A2,Orders!$A$2:$A$7,0)</f>
+        <v/>
+      </c>
+      <c r="D2">
+        <f>UPPER(LEFT(A2,3))&amp;"-"&amp;TEXT(B2,"0.00")</f>
+        <v/>
+      </c>
+      <c r="E2">
+        <f>EDATE(DATE(2026,1,31),ROW()-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gadget</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>VLOOKUP(A3,Orders!$A$2:$C$7,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="C3">
+        <f>MATCH(A3,Orders!$A$2:$A$7,0)</f>
+        <v/>
+      </c>
+      <c r="D3">
+        <f>UPPER(LEFT(A3,3))&amp;"-"&amp;TEXT(B3,"0.00")</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>EDATE(DATE(2026,1,31),ROW()-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gizmo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>VLOOKUP(A4,Orders!$A$2:$C$7,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="C4">
+        <f>MATCH(A4,Orders!$A$2:$A$7,0)</f>
+        <v/>
+      </c>
+      <c r="D4">
+        <f>UPPER(LEFT(A4,3))&amp;"-"&amp;TEXT(B4,"0.00")</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>EDATE(DATE(2026,1,31),ROW()-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Support plan</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>VLOOKUP(A5,Orders!$A$2:$C$7,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="C5">
+        <f>MATCH(A5,Orders!$A$2:$A$7,0)</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>UPPER(LEFT(A5,3))&amp;"-"&amp;TEXT(B5,"0.00")</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>EDATE(DATE(2026,1,31),ROW()-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Safe division</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>IFERROR(1/0,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Index/match</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>INDEX(Orders!$D$2:$D$7,MATCH("Gadget",Orders!$A$2:$A$7,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Discount (sheet name)</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>Discount</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -650,11 +926,11 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="B1" t="n">
-        <v>0.2</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -662,23 +938,215 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>125</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="B1">
+        <f>SUM(Jan:Mar!B1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D4">
+        <f>BudgetTable[[#This Row],[Actual]]-BudgetTable[[#This Row],[Plan]]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5200</v>
+      </c>
+      <c r="D5">
+        <f>BudgetTable[[#This Row],[Actual]]-BudgetTable[[#This Row],[Plan]]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>800</v>
+      </c>
+      <c r="C6" t="n">
+        <v>650</v>
+      </c>
+      <c r="D6">
+        <f>BudgetTable[[#This Row],[Actual]]-BudgetTable[[#This Row],[Plan]]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>SUBTOTAL(109,BudgetTable[Plan])</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>SUBTOTAL(109,BudgetTable[Actual])</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>SUBTOTAL(109,BudgetTable[Delta])</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>Orders total</t>
         </is>
       </c>
       <c r="B1">
-        <f>Orders!D7</f>
+        <f>Orders!D8</f>
         <v/>
       </c>
     </row>
@@ -689,7 +1157,40 @@
         </is>
       </c>
       <c r="B2">
-        <f>MAX(Orders!D2:D6)</f>
+        <f>MAX(Orders!D2:D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Products</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>COUNTA(OrderProducts)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Table total</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>SUM(OrderList[Total])</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Quarter budget</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>Budget!B1</f>
         <v/>
       </c>
     </row>

--- a/examples/03-formulas.xlsx
+++ b/examples/03-formulas.xlsx
@@ -85,6 +85,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="#,##0.00 [$UAH]"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -180,13 +191,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OrderList" displayName="OrderList" ref="A1:E7" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OrderList" displayName="OrderList" ref="A1:E7" headerRowCount="1" headerRowDxfId="0">
   <autoFilter ref="A1:E7"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Product"/>
     <tableColumn id="2" name="Quantity"/>
     <tableColumn id="3" name="Price"/>
-    <tableColumn id="4" name="Total"/>
+    <tableColumn id="4" name="Total" dataDxfId="1"/>
     <tableColumn id="5" name="Category"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
@@ -197,10 +208,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="BudgetTable" displayName="BudgetTable" ref="A3:D7" headerRowCount="1" totalsRowCount="1">
   <autoFilter ref="A3:D7"/>
   <tableColumns count="4">
-    <tableColumn id="1" name="Column1" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="Column2" totalsRowFunction="sum"/>
-    <tableColumn id="3" name="Column3" totalsRowFunction="sum"/>
-    <tableColumn id="4" name="Column4" totalsRowFunction="sum"/>
+    <tableColumn id="1" name="Item" totalsRowLabel="Total"/>
+    <tableColumn id="2" name="Plan" totalsRowFunction="sum"/>
+    <tableColumn id="3" name="Actual" totalsRowFunction="sum"/>
+    <tableColumn id="4" name="Delta" totalsRowFunction="sum"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
